--- a/tools/비표_양식.xlsx
+++ b/tools/비표_양식.xlsx
@@ -509,27 +509,27 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>· 비표대상 열에 O가 표시된 행만 비표 대상으로 처리합니다 (빈칸 행은 무시 — 위 박일반 예시)</v>
+        <v>· 이 파일을 관리자 화면의 (초대 명단과) 같은 업로드 칸에 올리면 자동으로 비표 명단으로 인식합니다</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>· 방문자명 + 연락처(뒤 4자리)로 초대 명단(대분류·연락처)과 자동 매칭됩니다</v>
+        <v>· 비표대상 열에 O 표시 행만 대상 (빈칸 행 무시)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>· 인원 = 수령할 비표 매수(빈칸이면 1)</v>
+        <v>· 방문자명 + 연락처(뒤 4자리)가 초대 명단의 대분류·연락처와 같아야 매칭됩니다</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>· 구역·좌석번호는 참고용(매칭에는 쓰지 않음)</v>
+        <v>· 인원 = 비표 매수(빈칸 1) · 구역·좌석번호는 참고용</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>· 관리자 화면에 올리면 즉시 반영, 대상자 티켓 확인 시 안내 팝업이 뜹니다</v>
+        <v>· 초대 명단보다 먼저 올려도 됩니다 — 명단 업로드 때 함께 반영</v>
       </c>
     </row>
   </sheetData>
